--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-durchfuehrung.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-durchfuehrung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$152</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5354" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Procedure|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Procedure|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -674,7 +674,7 @@
     <t>durchfuehrungsabsicht</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Durchfuehrungsabsicht|2026.0.1}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Durchfuehrungsabsicht|2027.0.0-ballot.rc1}
 </t>
   </si>
   <si>
@@ -702,7 +702,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-intend|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-intend|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Procedure.extension:durchfuehrungsabsicht.value[x].id</t>
@@ -1071,7 +1071,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-category-sct|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-category-sct|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Procedure.category.coding:sct.id</t>
@@ -1220,7 +1220,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/mii-vs-prozedur-ops|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/mii-vs-prozedur-ops|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.id</t>
@@ -1303,6 +1303,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -1819,6 +1822,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2379,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM151"/>
+  <dimension ref="A1:AM152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -2392,7 +2411,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.31640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="115.3046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4623,7 +4642,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>114</v>
@@ -4843,7 +4862,7 @@
         <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
@@ -10056,7 +10075,7 @@
         <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>114</v>
@@ -10387,7 +10406,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>114</v>
@@ -10605,7 +10624,7 @@
         <v>86</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>98</v>
@@ -10825,7 +10844,7 @@
         <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>114</v>
@@ -10938,7 +10957,7 @@
         <v>86</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>98</v>
@@ -11049,7 +11068,7 @@
         <v>86</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>98</v>
@@ -11100,7 +11119,9 @@
       <c r="M79" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N79" s="2"/>
+      <c r="N79" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O79" t="s" s="2">
         <v>245</v>
       </c>
@@ -11160,7 +11181,7 @@
         <v>86</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>98</v>
@@ -11177,10 +11198,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11211,7 +11232,9 @@
       <c r="M80" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N80" s="2"/>
+      <c r="N80" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O80" t="s" s="2">
         <v>252</v>
       </c>
@@ -11271,7 +11294,7 @@
         <v>86</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>98</v>
@@ -11288,10 +11311,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11384,7 +11407,7 @@
         <v>86</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>98</v>
@@ -11401,7 +11424,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>375</v>
@@ -11430,7 +11453,7 @@
         <v>127</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>228</v>
@@ -11446,7 +11469,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>77</v>
@@ -11497,7 +11520,7 @@
         <v>86</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>98</v>
@@ -11514,7 +11537,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>376</v>
@@ -11543,10 +11566,10 @@
         <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>238</v>
@@ -11608,7 +11631,7 @@
         <v>86</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>98</v>
@@ -11625,7 +11648,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>377</v>
@@ -11654,12 +11677,14 @@
         <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O84" t="s" s="2">
         <v>245</v>
       </c>
@@ -11674,7 +11699,7 @@
         <v>77</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>77</v>
@@ -11719,10 +11744,10 @@
         <v>86</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11736,7 +11761,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>378</v>
@@ -11770,7 +11795,9 @@
       <c r="M85" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N85" s="2"/>
+      <c r="N85" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O85" t="s" s="2">
         <v>252</v>
       </c>
@@ -11830,7 +11857,7 @@
         <v>86</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>98</v>
@@ -11847,7 +11874,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>379</v>
@@ -11943,7 +11970,7 @@
         <v>86</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>98</v>
@@ -11960,7 +11987,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>372</v>
@@ -12010,7 +12037,7 @@
         <v>77</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>77</v>
@@ -12029,7 +12056,7 @@
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>77</v>
@@ -12073,7 +12100,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>373</v>
@@ -12182,7 +12209,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>374</v>
@@ -12293,7 +12320,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>375</v>
@@ -12406,7 +12433,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>376</v>
@@ -12517,7 +12544,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>377</v>
@@ -12628,7 +12655,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>378</v>
@@ -12739,7 +12766,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>379</v>
@@ -12852,10 +12879,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12965,14 +12992,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12991,13 +13018,13 @@
         <v>87</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13048,7 +13075,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>86</v>
@@ -13063,21 +13090,21 @@
         <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13183,10 +13210,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13294,10 +13321,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13323,13 +13350,13 @@
         <v>100</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13379,7 +13406,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13388,7 +13415,7 @@
         <v>86</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>98</v>
@@ -13405,10 +13432,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13434,13 +13461,13 @@
         <v>127</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13469,10 +13496,10 @@
         <v>143</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>77</v>
@@ -13490,7 +13517,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13516,10 +13543,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13545,13 +13572,13 @@
         <v>270</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13601,7 +13628,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13627,10 +13654,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13656,13 +13683,13 @@
         <v>100</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13712,7 +13739,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13738,10 +13765,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13764,16 +13791,16 @@
         <v>87</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13823,7 +13850,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13838,21 +13865,21 @@
         <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13958,10 +13985,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14069,10 +14096,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14098,13 +14125,13 @@
         <v>100</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14154,7 +14181,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14163,7 +14190,7 @@
         <v>86</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>98</v>
@@ -14180,10 +14207,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14209,13 +14236,13 @@
         <v>127</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14244,10 +14271,10 @@
         <v>143</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>77</v>
@@ -14265,7 +14292,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14291,10 +14318,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14320,13 +14347,13 @@
         <v>270</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14376,7 +14403,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14402,10 +14429,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14431,13 +14458,13 @@
         <v>100</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14487,7 +14514,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14513,10 +14540,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14539,16 +14566,16 @@
         <v>87</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14586,17 +14613,17 @@
         <v>77</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14611,24 +14638,24 @@
         <v>98</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
@@ -14653,13 +14680,13 @@
         <v>205</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14709,7 +14736,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14724,24 +14751,24 @@
         <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>77</v>
@@ -14763,16 +14790,16 @@
         <v>87</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14822,7 +14849,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14837,21 +14864,21 @@
         <v>98</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14874,13 +14901,13 @@
         <v>87</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14931,7 +14958,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14949,7 +14976,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14957,10 +14984,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14983,13 +15010,13 @@
         <v>87</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15040,7 +15067,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15058,7 +15085,7 @@
         <v>77</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>77</v>
@@ -15066,10 +15093,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15092,13 +15119,13 @@
         <v>87</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15149,7 +15176,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15164,7 +15191,7 @@
         <v>98</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>77</v>
@@ -15175,10 +15202,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15284,10 +15311,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15395,14 +15422,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15424,10 +15451,10 @@
         <v>106</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>109</v>
@@ -15482,7 +15509,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15508,10 +15535,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15537,14 +15564,14 @@
         <v>310</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15572,10 +15599,10 @@
         <v>151</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
@@ -15593,7 +15620,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15608,21 +15635,21 @@
         <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15645,17 +15672,17 @@
         <v>87</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15704,7 +15731,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>86</v>
@@ -15719,21 +15746,21 @@
         <v>98</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15756,17 +15783,17 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>77</v>
@@ -15815,7 +15842,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15841,10 +15868,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15867,17 +15894,17 @@
         <v>87</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -15926,7 +15953,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15944,7 +15971,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15952,10 +15979,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15981,13 +16008,13 @@
         <v>310</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16016,10 +16043,10 @@
         <v>151</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16037,7 +16064,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16052,10 +16079,10 @@
         <v>98</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -16063,10 +16090,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16089,16 +16116,16 @@
         <v>87</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16148,7 +16175,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16163,10 +16190,10 @@
         <v>98</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
@@ -16174,10 +16201,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16203,13 +16230,13 @@
         <v>310</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16238,10 +16265,10 @@
         <v>151</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>77</v>
@@ -16259,7 +16286,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16280,15 +16307,15 @@
         <v>77</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16394,10 +16421,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16505,12 +16532,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="C128" s="2"/>
+      <c r="C128" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>77</v>
       </c>
@@ -16519,32 +16548,28 @@
         <v>78</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>139</v>
+        <v>581</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>326</v>
+        <v>582</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>77</v>
       </c>
@@ -16580,17 +16605,19 @@
         <v>77</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AC128" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>331</v>
+        <v>113</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16602,7 +16629,7 @@
         <v>77</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>77</v>
@@ -16611,19 +16638,17 @@
         <v>77</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>77</v>
       </c>
@@ -16632,7 +16657,7 @@
         <v>78</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>87</v>
@@ -16647,10 +16672,10 @@
         <v>139</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>328</v>
@@ -16666,7 +16691,7 @@
         <v>77</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>582</v>
+        <v>77</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>77</v>
@@ -16693,16 +16718,14 @@
         <v>77</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AF129" t="s" s="2">
         <v>331</v>
@@ -16729,14 +16752,16 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="C130" s="2"/>
+      <c r="C130" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="D130" t="s" s="2">
         <v>77</v>
       </c>
@@ -16748,25 +16773,29 @@
         <v>86</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
       </c>
@@ -16775,7 +16804,7 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>77</v>
+        <v>588</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>77</v>
@@ -16814,19 +16843,19 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>103</v>
+        <v>331</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>77</v>
@@ -16835,26 +16864,26 @@
         <v>77</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>77</v>
@@ -16866,17 +16895,15 @@
         <v>77</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -16913,31 +16940,31 @@
         <v>77</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>77</v>
@@ -16949,48 +16976,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>77</v>
       </c>
@@ -16999,7 +17024,7 @@
         <v>77</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>77</v>
@@ -17026,31 +17051,31 @@
         <v>77</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>77</v>
@@ -17059,15 +17084,15 @@
         <v>77</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17075,7 +17100,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>86</v>
@@ -17090,18 +17115,20 @@
         <v>87</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
       </c>
@@ -17110,7 +17137,7 @@
         <v>77</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>77</v>
@@ -17149,7 +17176,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17170,15 +17197,15 @@
         <v>77</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17186,7 +17213,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>86</v>
@@ -17201,18 +17228,18 @@
         <v>87</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>77</v>
       </c>
@@ -17260,7 +17287,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17281,15 +17308,15 @@
         <v>77</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17297,13 +17324,13 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>77</v>
@@ -17312,17 +17339,17 @@
         <v>87</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -17371,7 +17398,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17392,15 +17419,15 @@
         <v>77</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17423,19 +17450,17 @@
         <v>87</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>257</v>
+        <v>100</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>77</v>
@@ -17484,7 +17509,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17505,15 +17530,15 @@
         <v>77</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17536,19 +17561,19 @@
         <v>87</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>100</v>
+        <v>257</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>355</v>
+        <v>259</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>357</v>
+        <v>261</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>77</v>
@@ -17597,7 +17622,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>358</v>
+        <v>262</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -17618,15 +17643,15 @@
         <v>77</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>359</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17649,18 +17674,20 @@
         <v>87</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>599</v>
+        <v>354</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>600</v>
+        <v>355</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O138" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
       </c>
@@ -17684,13 +17711,13 @@
         <v>77</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>602</v>
+        <v>77</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>603</v>
+        <v>77</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>77</v>
@@ -17708,7 +17735,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>598</v>
+        <v>358</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -17729,7 +17756,7 @@
         <v>77</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
     </row>
     <row r="139" hidden="true">
@@ -17748,7 +17775,7 @@
         <v>78</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>77</v>
@@ -17757,19 +17784,19 @@
         <v>77</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -17795,13 +17822,13 @@
         <v>77</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>77</v>
+        <v>608</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>77</v>
+        <v>609</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>77</v>
@@ -17825,7 +17852,7 @@
         <v>78</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>77</v>
@@ -17845,10 +17872,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17871,16 +17898,16 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>310</v>
+        <v>611</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -17906,13 +17933,13 @@
         <v>77</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>613</v>
+        <v>77</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>614</v>
+        <v>77</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>77</v>
@@ -17930,7 +17957,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -17982,18 +18009,18 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="N141" s="2"/>
-      <c r="O141" t="s" s="2">
-        <v>619</v>
-      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>77</v>
       </c>
@@ -18017,13 +18044,13 @@
         <v>77</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>77</v>
+        <v>619</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>77</v>
@@ -18067,10 +18094,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18093,16 +18120,18 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>310</v>
+        <v>622</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+      <c r="O142" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
       </c>
@@ -18126,13 +18155,13 @@
         <v>77</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>623</v>
+        <v>77</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>624</v>
+        <v>77</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>77</v>
@@ -18150,7 +18179,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18174,12 +18203,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18193,7 +18222,7 @@
         <v>79</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>77</v>
@@ -18202,7 +18231,7 @@
         <v>77</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>626</v>
+        <v>310</v>
       </c>
       <c r="L143" t="s" s="2">
         <v>627</v>
@@ -18235,13 +18264,13 @@
         <v>77</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>77</v>
+        <v>630</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>77</v>
@@ -18259,7 +18288,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18274,16 +18303,16 @@
         <v>98</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>629</v>
+        <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>630</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
         <v>631</v>
       </c>
@@ -18302,7 +18331,7 @@
         <v>79</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>77</v>
@@ -18311,13 +18340,13 @@
         <v>77</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>517</v>
+        <v>632</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -18383,21 +18412,21 @@
         <v>98</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>77</v>
+        <v>635</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>77</v>
+        <v>636</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18408,7 +18437,7 @@
         <v>78</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>77</v>
@@ -18420,13 +18449,13 @@
         <v>77</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>100</v>
+        <v>518</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>101</v>
+        <v>638</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>102</v>
+        <v>639</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18477,19 +18506,19 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>77</v>
@@ -18503,21 +18532,21 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>77</v>
@@ -18529,17 +18558,15 @@
         <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>77</v>
@@ -18588,19 +18615,19 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>77</v>
@@ -18614,14 +18641,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>524</v>
+        <v>105</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -18634,26 +18661,24 @@
         <v>77</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>525</v>
+        <v>107</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>526</v>
+        <v>108</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O147" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>77</v>
       </c>
@@ -18701,7 +18726,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>527</v>
+        <v>113</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -18727,42 +18752,46 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>77</v>
+        <v>525</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>310</v>
+        <v>106</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>638</v>
+        <v>526</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
       </c>
@@ -18786,13 +18815,13 @@
         <v>77</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>640</v>
+        <v>77</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>641</v>
+        <v>77</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>77</v>
@@ -18810,19 +18839,19 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>637</v>
+        <v>528</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>77</v>
@@ -18836,10 +18865,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18847,7 +18876,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>86</v>
@@ -18862,7 +18891,7 @@
         <v>77</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>643</v>
+        <v>310</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>644</v>
@@ -18895,13 +18924,13 @@
         <v>77</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>77</v>
+        <v>646</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>77</v>
+        <v>647</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>77</v>
@@ -18919,10 +18948,10 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>86</v>
@@ -18943,12 +18972,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18959,10 +18988,10 @@
         <v>86</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>77</v>
@@ -18971,20 +19000,16 @@
         <v>77</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>650</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>77</v>
       </c>
@@ -19032,13 +19057,13 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>77</v>
@@ -19056,12 +19081,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19069,13 +19094,13 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>77</v>
@@ -19084,18 +19109,20 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>310</v>
+        <v>649</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O151" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
       </c>
@@ -19119,13 +19146,13 @@
         <v>77</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>654</v>
+        <v>77</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>655</v>
+        <v>77</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>77</v>
@@ -19143,7 +19170,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19167,8 +19194,119 @@
         <v>77</v>
       </c>
     </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM151">
+  <autoFilter ref="A1:AM152">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19178,7 +19316,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI150">
+  <conditionalFormatting sqref="A2:AI151">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
